--- a/data/trans_camb/P1435-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P1435-Clase-trans_camb.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,92</t>
+          <t>1,63</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,92</t>
+          <t>1,63</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 1,06</t>
+          <t>-6,38; 0,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,18; -0,29</t>
+          <t>-7,13; -0,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 5,74</t>
+          <t>-2,85; 5,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 1,06</t>
+          <t>-6,38; 0,7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,18; -0,29</t>
+          <t>-7,13; -0,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 5,74</t>
+          <t>-2,85; 5,09</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>22,73%</t>
         </is>
       </c>
     </row>
@@ -710,32 +710,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-67,6; 23,15</t>
+          <t>-70,68; 15,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-76,72; -1,71</t>
+          <t>-78,73; -4,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-24,31; 117,13</t>
+          <t>-31,4; 99,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-67,6; 23,15</t>
+          <t>-70,68; 15,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-76,72; -1,71</t>
+          <t>-78,73; -4,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-24,31; 117,13</t>
+          <t>-31,4; 99,83</t>
         </is>
       </c>
     </row>
@@ -762,7 +762,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-5,84</t>
+          <t>-5,79</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-5,84</t>
+          <t>-5,79</t>
         </is>
       </c>
     </row>
@@ -790,32 +790,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-13,08; -4,26</t>
+          <t>-12,63; -4,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-14,03; -5,8</t>
+          <t>-13,93; -5,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,13; -1,81</t>
+          <t>-10,35; -1,81</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-13,08; -4,26</t>
+          <t>-12,63; -4,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-14,03; -5,8</t>
+          <t>-13,93; -5,97</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-10,13; -1,81</t>
+          <t>-10,35; -1,81</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-43,13%</t>
+          <t>-42,76%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-43,13%</t>
+          <t>-42,76%</t>
         </is>
       </c>
     </row>
@@ -866,32 +866,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-78,57; -36,93</t>
+          <t>-77,84; -36,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-85,55; -51,38</t>
+          <t>-85,66; -52,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-62,45; -13,87</t>
+          <t>-61,23; -14,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-78,57; -36,93</t>
+          <t>-77,84; -36,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-85,55; -51,38</t>
+          <t>-85,66; -52,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-62,45; -13,87</t>
+          <t>-61,23; -14,8</t>
         </is>
       </c>
     </row>
@@ -918,7 +918,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-5,36</t>
+          <t>-4,66</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-5,36</t>
+          <t>-4,66</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,53; -0,7</t>
+          <t>-11,87; -1,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,28; -1,65</t>
+          <t>-13,51; -2,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,08; -0,21</t>
+          <t>-10,37; 0,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-11,53; -0,7</t>
+          <t>-11,87; -1,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-12,28; -1,65</t>
+          <t>-13,51; -2,5</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-11,08; -0,21</t>
+          <t>-10,37; 0,41</t>
         </is>
       </c>
     </row>
@@ -994,7 +994,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-57,36%</t>
+          <t>-49,94%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-57,36%</t>
+          <t>-49,94%</t>
         </is>
       </c>
     </row>
@@ -1022,32 +1022,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-84,99; 0,6</t>
+          <t>-86,66; -7,27</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-93,68; -19,03</t>
+          <t>-94,21; -29,55</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-83,49; 10,16</t>
+          <t>-78,43; 12,22</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-84,99; 0,6</t>
+          <t>-86,66; -7,27</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-93,68; -19,03</t>
+          <t>-94,21; -29,55</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-83,49; 10,16</t>
+          <t>-78,43; 12,22</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-3,74</t>
+          <t>-1,84</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-3,74</t>
+          <t>-1,84</t>
         </is>
       </c>
     </row>
@@ -1102,32 +1102,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,46; -2,16</t>
+          <t>-7,65; -2,21</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-10,78; -6,43</t>
+          <t>-11,01; -6,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,88; -0,77</t>
+          <t>-4,47; 1,05</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,46; -2,16</t>
+          <t>-7,65; -2,21</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-10,78; -6,43</t>
+          <t>-11,01; -6,38</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,88; -0,77</t>
+          <t>-4,47; 1,05</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-38,67%</t>
+          <t>-18,98%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-38,67%</t>
+          <t>-18,98%</t>
         </is>
       </c>
     </row>
@@ -1178,32 +1178,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-66,3; -23,53</t>
+          <t>-66,85; -25,2</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-94,02; -77,54</t>
+          <t>-94,9; -77,84</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-71,22; -11,09</t>
+          <t>-40,59; 12,92</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-66,3; -23,53</t>
+          <t>-66,85; -25,2</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-94,02; -77,54</t>
+          <t>-94,9; -77,84</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-71,22; -11,09</t>
+          <t>-40,59; 12,92</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7,74</t>
+          <t>0,24</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,74</t>
+          <t>0,24</t>
         </is>
       </c>
     </row>
@@ -1258,32 +1258,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 0,04</t>
+          <t>-4,29; 0,17</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,93; -0,65</t>
+          <t>-5,06; -0,8</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 30,1</t>
+          <t>-2,07; 2,53</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 0,04</t>
+          <t>-4,29; 0,17</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,93; -0,65</t>
+          <t>-5,06; -0,8</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 30,1</t>
+          <t>-2,07; 2,53</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>159,57%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>159,57%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -1334,39 +1334,39 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-67,48; 6,5</t>
+          <t>-68,29; 6,85</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-77,47; -15,47</t>
+          <t>-78,25; -22,65</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-18,17; 844,29</t>
+          <t>-32,44; 77,27</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-67,48; 6,5</t>
+          <t>-68,29; 6,85</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-77,47; -15,47</t>
+          <t>-78,25; -22,65</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-18,17; 844,29</t>
+          <t>-32,44; 77,27</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-2,93</t>
+          <t>-2,85</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-2,93</t>
+          <t>-2,85</t>
         </is>
       </c>
     </row>
@@ -1414,32 +1414,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4,39; -0,89</t>
+          <t>-4,25; -0,79</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-6,62; -3,65</t>
+          <t>-6,5; -3,65</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-5,04; -0,72</t>
+          <t>-4,93; -0,71</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-4,39; -0,89</t>
+          <t>-4,25; -0,79</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-6,62; -3,65</t>
+          <t>-6,5; -3,65</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-5,04; -0,72</t>
+          <t>-4,93; -0,71</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-48,48%</t>
+          <t>-47,17%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-48,48%</t>
+          <t>-47,17%</t>
         </is>
       </c>
     </row>
@@ -1490,32 +1490,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-62,77; -17,28</t>
+          <t>-61,34; -14,22</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-91,27; -68,27</t>
+          <t>-91,11; -67,82</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-73,06; -11,55</t>
+          <t>-71,14; -11,59</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-62,77; -17,28</t>
+          <t>-61,34; -14,22</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-91,27; -68,27</t>
+          <t>-91,11; -67,82</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-73,06; -11,55</t>
+          <t>-71,14; -11,59</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-0,31</t>
+          <t>-1,62</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-0,31</t>
+          <t>-1,62</t>
         </is>
       </c>
     </row>
@@ -1570,32 +1570,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-4,99; -2,73</t>
+          <t>-4,91; -2,7</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-6,88; -4,85</t>
+          <t>-6,87; -4,89</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 8,51</t>
+          <t>-2,82; -0,3</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-4,99; -2,73</t>
+          <t>-4,91; -2,7</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-6,88; -4,85</t>
+          <t>-6,87; -4,89</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 8,51</t>
+          <t>-2,82; -0,3</t>
         </is>
       </c>
     </row>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-4,08%</t>
+          <t>-21,0%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-4,08%</t>
+          <t>-21,0%</t>
         </is>
       </c>
     </row>
@@ -1646,32 +1646,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-59,01; -37,99</t>
+          <t>-59,03; -37,95</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-81,54; -67,94</t>
+          <t>-81,07; -67,99</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-32,85; 118,49</t>
+          <t>-33,57; -4,15</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-59,01; -37,99</t>
+          <t>-59,03; -37,95</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-81,54; -67,94</t>
+          <t>-81,07; -67,99</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-32,85; 118,49</t>
+          <t>-33,57; -4,15</t>
         </is>
       </c>
     </row>
